--- a/光伏配储项目/电价数据/2026/珠海站.xlsx
+++ b/光伏配储项目/电价数据/2026/珠海站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.55362</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.52067</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8643</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.1271</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.02214</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.72326</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.73262</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5403600000000001</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.59256</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52595</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.69539</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.69552</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.6860499999999999</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.7127899999999999</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.70331</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.6670900000000001</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.69202</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.5294800000000001</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.70605</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.5480499999999999</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.70416</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.55367</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.73691</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.82631</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85875</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67711</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.67225</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7343200000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7570399999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.01083</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99539</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08632</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75061</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.6984600000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7837499999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.95063</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31314</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52323</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.76034</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76825</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74786</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9288200000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.8953099999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04853</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31597</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12509</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.12467</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.73441</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.21119</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16958</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09692</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22922</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.5351</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10704</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.24812</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47673</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30585</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23652</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.41118</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35464</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28534</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.80365</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16861</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03724</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61591</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.51619</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.5902200000000001</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48828</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.5255299999999999</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.5063799999999999</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51638</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.5123300000000001</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.56141</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.77199</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.0773</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.84163</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5936</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48728</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.54064</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.51042</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.93562</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.1513</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7764099999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11999</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03806</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.9876200000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7082000000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54806</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.56708</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6800499999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15486</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.23179</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47597</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15902</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.63004</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07876</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.81863</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25173</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13667</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28345</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62173</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.63866</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.57023</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.16203</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16912</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17775</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17227</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9691000000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18748</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20231</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19407</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66903</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16232</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20563</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.21174</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50809</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.41344</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16856</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50938</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26404</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.74342</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7647999999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9153</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6047</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6877000000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6963400000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53428</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5796</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.50946</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.84905</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.60054</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.59253</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.5608500000000001</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.55992</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.63815</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.58845</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57757</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.52528</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49896</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.51434</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.5012</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.5111100000000001</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69311</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.8309</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10818</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.87393</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7453</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70336</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.6045199999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6428700000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72949</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.16475</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52267</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6774199999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16739</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.62218</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.18786</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.16585</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.79314</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.94038</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16481</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.1662</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8925299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5595599999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47469</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67435</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16597</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02896</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16528</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39383</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23685</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16651</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.21584</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20954</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.40237</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26931</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28621</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.6489</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.17244</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.1751</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78546</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03973</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07889</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09975</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08582</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20526</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16873</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24906</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.9955499999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.75461</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7111799999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.7244700000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.71727</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.21488</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6827799999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.8567100000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.5430199999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.62511</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.24298</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.59678</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5909099999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.53122</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.51342</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.5126499999999999</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.52458</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.5813200000000001</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.4968399999999999</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.46192</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.49047</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6765800000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93286</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16834</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30969</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.55207</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66594</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90379</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86524</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16447</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43987</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77272</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.95392</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20577</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.68955</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12228</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.5225599999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48537</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65455</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.9967200000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.10306</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24938</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16907</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.06191</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98246</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02587</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98982</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25267</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.44182</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7935099999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34929</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.24864</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.19207</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.8479500000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07475</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.16138</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12179</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15471</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.25533</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31871</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15473</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.27012</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18803</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18613</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18908</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.18999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17551</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15306</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17624</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.72427</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7265499999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32163</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74374</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47782</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52312</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71663</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84797</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6149600000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70182</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.72688</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8455199999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70531</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55087</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54991</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53864</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.59249</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47072</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08565</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55002</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48236</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.51236</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46634</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63352</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48324</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48753</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5945499999999999</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.50558</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50595</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40822</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.19151</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9665900000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9823999999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.59045</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.64898</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.5482100000000001</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.53113</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54706</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.51651</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.51527</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.69237</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.53073</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.53104</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.51398</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.51481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.51554</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07339</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08284999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04499</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04707</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00294</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04665</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04628</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44596</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.59538</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.54216</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.56377</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.5439400000000001</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.5431699999999999</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55936</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.7421</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8749</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67504</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.6490199999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.66786</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.7489400000000001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93991</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.73027</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73198</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.88839</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63234</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44923</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08563</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.73187</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7286699999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.6390800000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60315</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7287400000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.78871</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78287</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74197</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.0183</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40665</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.84345</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43446</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.29871</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.78915</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.38114</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04539</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.40142</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76577</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.44436</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.77462</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7850499999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50199</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4114</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21851</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54123</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.61852</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5862999999999999</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.56686</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.57533</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.58185</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5833700000000001</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.56338</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.47149</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49417</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.51752</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.52103</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.55279</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.5186499999999999</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.56839</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.47345</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.57569</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4942</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43727</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5637000000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66625</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07964</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.63873</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59865</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00157</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33906</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30671</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27474</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.55928</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.8017000000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5730599999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55075</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95704</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77678</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72588</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57553</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.93426</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.79038</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5428099999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.67228</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.5909800000000001</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.67218</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6234400000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6644099999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7067</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6419199999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.66306</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58374</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57809</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.66113</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67813</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.62482</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.67195</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.69004</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.76173</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.68089</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.7588200000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.6899299999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.6877300000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.6892200000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.67357</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.6633600000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.66255</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.6064700000000001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.60963</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.5585800000000001</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.58299</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.56003</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.5456</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.53544</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.47084</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57752</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.61286</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62551</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.68341</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.5376299999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.55125</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49419</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64218</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.51348</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6179199999999999</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72819</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.8719600000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11251</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93233</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5453600000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11362</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.84414</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.85981</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.64002</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.81032</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.06805</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.57182</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43233</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.87566</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.9976499999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.1916</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78426</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.8139299999999999</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.74305</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7401799999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47519</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44326</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19623</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51272</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7933600000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74949</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16657</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92167</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.64342</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66999</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7010299999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55544</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.16429</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61286</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90952</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57733</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.57639</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33816</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.26266</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.23047</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.34804</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00996</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.5195</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60238</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85927</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50623</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.75054</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07618</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07415</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9070900000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.9830800000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93672</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17428</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15485</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8630399999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.1561</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60812</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9711000000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01629</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15552</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.95096</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.99125</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58513</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.9246799999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98197</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08952</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.8860800000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87371</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79395</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09706</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55695</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.99193</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33182</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.61124</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49685</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.50901</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44708</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.5954700000000001</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.50292</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.48278</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.5345800000000001</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83312</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71448</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.5534199999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.57012</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.73509</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8664500000000001</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.57228</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.57636</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57812</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.51297</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.5127699999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.5604600000000001</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.6211599999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.56535</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.5721799999999999</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46419</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67749</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54387</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50804</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.51137</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56862</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.47097</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.5756100000000001</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5318099999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.5382899999999999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.52567</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.55215</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.52639</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.52688</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.48793</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.47546</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45774</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5542100000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28154</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47015</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70129</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60301</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62767</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.84897</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27141</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16633</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8521599999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70138</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9402</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16791</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12161</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01849</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54186</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44603</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5632699999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.46426</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.46427</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50701</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43975</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.44326</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.4871</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.51173</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.58236</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.7279</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.06541</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11566</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.99139</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98011</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98165</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56576</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54731</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94624</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08617</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.78444</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01318</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.76844</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64901</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64175</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70905</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79995</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29838</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.73019</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.31985</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.11461</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9412699999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.60951</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62445</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65809</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67146</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66653</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.6435</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20688</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70092</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78272</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69823</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70601</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71417</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63368</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74846</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02162</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.1314</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69207</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70051</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69428</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77391</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72407</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81345</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.66675</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.06803</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.46889</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.58226</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45914</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.49199</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34417</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.60223</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17917</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.5048</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.49287</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46598</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.5135299999999999</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44531</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74733</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49508</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51083</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51908</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45221</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.9226599999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47512</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18009</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90222</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7631699999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49765</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7469199999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.5152100000000001</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68166</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49604</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66489</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44928</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6517999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5258200000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.49087</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48595</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.71174</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.4431</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7614500000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.7681399999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48006</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50159</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7230700000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7625599999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5542100000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50182</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02049</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48712</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44681</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.0948</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12975</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.0837</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11232</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.1288</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01859</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19438</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14265</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13185</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.17437</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84139</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19128</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8484400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34115</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90376</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73272</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75771</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94896</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.70694</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.39494</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.56624</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.54499</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.5339400000000001</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.54047</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75619</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.35834</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.5199600000000001</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.62017</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.61442</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.51507</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.58078</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.5965499999999999</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.59768</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.5204099999999999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.59246</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.58108</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.5073299999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46373</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47124</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.47119</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.50552</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.64015</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5006700000000001</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68552</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5398999999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.0295</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77412</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74174</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.28032</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34177</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.71847</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64192</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34842</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.9950399999999999</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59216</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49476</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5394800000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59002</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7338300000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17752</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.69136</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91306</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.66512</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9347000000000001</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.88106</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74529</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71459</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17569</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17688</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42573</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23692</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.6175</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20573</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28301</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07794</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.3997</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03335</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.6721699999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.6423099999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43076</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.14148</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63417</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5062099999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45233</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80069</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.66883</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.65006</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50846</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06842</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66724</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66336</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7960900000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04969</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16787</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49948</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19242</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5460199999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15343</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5567300000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57168</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42787</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45938</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51127</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46052</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59736</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.75648</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12784</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.69147</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55662</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49323</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45512</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44767</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44504</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58085</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47774</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46209</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46318</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.54561</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45969</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4193</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49676</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48487</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50287</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.46453</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37035</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.86437</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40658</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42335</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.11281</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.7005399999999999</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17457</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.26044</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09961</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6887000000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55903</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49197</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8023400000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38258</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.4658</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.48448</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09343</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36644</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.8526</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.80967</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52181</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.75337</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75202</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.4157</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44148</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55433</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.51291</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.7495499999999999</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.5754400000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.79747</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7532000000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5229299999999999</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28842</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.29178</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21781</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06209</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9550700000000001</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28517</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6117</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5446299999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5756100000000001</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.75009</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54604</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5413600000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75307</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75146</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.57539</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49194</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98617</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75979</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6185900000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.75061</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17353</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72768</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62454</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.2373</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.87415</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.8595700000000001</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.88103</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.89962</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15348</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6391100000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.93231</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.6792999999999999</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95733</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.62071</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63884</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73641</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.62119</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79336</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24434</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.0343</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.99652</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00886</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51537</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34145</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.04833</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7541</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34524</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55688</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5497799999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75105</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75285</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5904700000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.55662</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.53753</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44809</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47362</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49474</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55724</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81151</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.1542</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11955</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03246</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12227</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.72633</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.72108</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04329</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06167</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66879</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55544</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56191</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.55014</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28218</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5464600000000001</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55138</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54125</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65724</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54201</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04355</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.65434</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54673</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49707</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48038</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49805</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5551200000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55862</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49601</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51169</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42231</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49845</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.55847</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6572100000000001</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.15298</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05596</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6584099999999999</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5800299999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15121</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.86376</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6576799999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.14083</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81359</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53291</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34434</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.71469</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.58345</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.73197</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5534</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4189</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38722</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62588</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5835499999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62995</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00538</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17595</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.92452</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.96196</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.01088</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95201</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91839</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94831</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9321799999999999</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91557</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9178999999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6735599999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02875</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6702400000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.02562</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12706</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10892</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69967</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.84333</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.91022</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54194</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66739</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68987</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73827</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78834</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.19723</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07735</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01686</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32941</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01251</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11159</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91598</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.75201</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.75126</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8135800000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6921499999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69068</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55655</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.68843</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.72503</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68533</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7473099999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69545</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50559</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.99519</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00842</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8972100000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01623</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.99907</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.99925</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16728</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.0685</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.09388</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66595</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5963200000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71845</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70547</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02559</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.69853</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75155</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13521</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.23363</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.43499</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.20353</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.36569</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.98705</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40356</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.38283</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.74648</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65718</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.42468</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42649</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.8076100000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7555499999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8021200000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75422</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8109500000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31344</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00392</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9340499999999999</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.96027</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03403</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16264</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06231</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86427</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69341</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22318</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20888</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20955</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.15175</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86752</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7034900000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09711</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10804</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10807</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13446</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10577</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52059</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20108</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.64062</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57787</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73203</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.66416</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18512</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.8623200000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06614</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03368</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.05143</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.0364</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06911</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12811</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05059</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06119</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18419</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16274</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21655</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20332</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26751</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16942</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14419</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10063</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12678</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17649</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19407</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17465</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07814</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6745800000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61499</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5660299999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.54857</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53138</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31356</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31077</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06771</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44478</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44278</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.41927</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84834</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5669299999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68447</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.70011</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.6517500000000001</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9419099999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7529400000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9472699999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15904</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30713</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44645</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.43452</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45936</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54664</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25286</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8511799999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.62126</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73356</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7006</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50279</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.8443200000000001</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8670800000000001</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.21593</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77332</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.5799299999999999</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58077</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62781</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.70831</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58404</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.73586</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.61081</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.20048</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17701</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41157</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.1784</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17902</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.18436</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10454</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07926</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20742</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10692</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19322</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05189</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08334</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20649</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08359</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54277</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.80751</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56402</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21429</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8491000000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8496</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55911</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5545599999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56257</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51547</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539299999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.52119</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49518</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.4992</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.54777</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.52028</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5575599999999999</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17561</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88298</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.4939</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17241</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50938</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.56947</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84421</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951900000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8528600000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.5437799999999999</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17758</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70097</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55532</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.17416</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54922</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.55033</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5807599999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79959</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79904</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.8490700000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17419</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7986599999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68353</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05322</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17489</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.17611</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.1776</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17552</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.73262</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64554</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.67706</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68509</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73124</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83474</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81797</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80711</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.75678</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13701</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.7514299999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6094400000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63695</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.63873</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61464</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7044</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67099</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81433</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7040700000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.6081299999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
